--- a/events.xlsx
+++ b/events.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="QhhNt3ND42fd+j5kcS+YjbaMC9p7RudKTHZbSQt82Wc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="b8yL2kWxQclk0lTATQPPImx8IuoRrNodS6HkMoOKXP4="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="55">
   <si>
     <t>title</t>
   </si>
@@ -154,6 +154,30 @@
   </si>
   <si>
     <t>いちのせき健康の森</t>
+  </si>
+  <si>
+    <t>太白区中央市民センター 体育館</t>
+  </si>
+  <si>
+    <t>若林区文化センター 展示ホール</t>
+  </si>
+  <si>
+    <t>泉海洋センター</t>
+  </si>
+  <si>
+    <t>大会</t>
+  </si>
+  <si>
+    <t>チャンバラ大会</t>
+  </si>
+  <si>
+    <t>水の森市民センター 体育館</t>
+  </si>
+  <si>
+    <t>体験会</t>
+  </si>
+  <si>
+    <t>夏の体験会</t>
   </si>
   <si>
     <t>夏祭り</t>
@@ -8910,44 +8934,556 @@
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C109" s="7">
+        <v>46238.72222222222</v>
+      </c>
+      <c r="D109" s="7">
+        <v>46238.76388888889</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" s="7">
+        <v>46252.72222222222</v>
+      </c>
+      <c r="D110" s="7">
+        <v>46252.76388888889</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C111" s="7">
+        <v>46259.72222222222</v>
+      </c>
+      <c r="D111" s="7">
+        <v>46259.76388888889</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C113" s="7">
+        <v>46239.708333333336</v>
+      </c>
+      <c r="D113" s="7">
+        <v>46239.75</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C114" s="7">
+        <v>46246.708333333336</v>
+      </c>
+      <c r="D114" s="7">
+        <v>46246.739583333336</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C115" s="7">
+        <v>46246.739583333336</v>
+      </c>
+      <c r="D115" s="7">
+        <v>46246.770833333336</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C116" s="7">
+        <v>46253.708333333336</v>
+      </c>
+      <c r="D116" s="7">
+        <v>46253.75</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C117" s="7">
+        <v>46260.708333333336</v>
+      </c>
+      <c r="D117" s="7">
+        <v>46260.739583333336</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" s="7">
+        <v>46260.739583333336</v>
+      </c>
+      <c r="D118" s="7">
+        <v>46260.770833333336</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" s="7">
+        <v>46240.708333333336</v>
+      </c>
+      <c r="D120" s="7">
+        <v>46240.75</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C121" s="7">
+        <v>46247.708333333336</v>
+      </c>
+      <c r="D121" s="7">
+        <v>46247.75</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C122" s="7">
+        <v>46254.708333333336</v>
+      </c>
+      <c r="D122" s="7">
+        <v>46254.75</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C123" s="7">
+        <v>46261.729166666664</v>
+      </c>
+      <c r="D123" s="7">
+        <v>46261.770833333336</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C125" s="7">
+        <v>46241.666666666664</v>
+      </c>
+      <c r="D125" s="7">
+        <v>46241.70138888889</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C126" s="7">
+        <v>46255.666666666664</v>
+      </c>
+      <c r="D126" s="7">
+        <v>46255.70138888889</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C127" s="7">
+        <v>46262.666666666664</v>
+      </c>
+      <c r="D127" s="7">
+        <v>46262.70138888889</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C129" s="7">
+        <v>46242.625</v>
+      </c>
+      <c r="D129" s="7">
+        <v>46242.666666666664</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C130" s="7">
+        <v>46249.625</v>
+      </c>
+      <c r="D130" s="7">
+        <v>46249.65625</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C131" s="7">
+        <v>46249.666666666664</v>
+      </c>
+      <c r="D131" s="7">
+        <v>46249.697916666664</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C132" s="7">
+        <v>46256.625</v>
+      </c>
+      <c r="D132" s="7">
+        <v>46256.65625</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" s="7">
+        <v>46256.666666666664</v>
+      </c>
+      <c r="D133" s="7">
+        <v>46256.697916666664</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" s="7">
+        <v>46243.416666666664</v>
+      </c>
+      <c r="D135" s="7">
+        <v>46243.458333333336</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C136" s="7">
+        <v>46257.416666666664</v>
+      </c>
+      <c r="D136" s="7">
+        <v>46257.458333333336</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C137" s="7">
+        <v>46264.416666666664</v>
+      </c>
+      <c r="D137" s="7">
+        <v>46264.458333333336</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
     <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C139" s="7">
+        <v>46242.395833333336</v>
+      </c>
+      <c r="D139" s="7">
+        <v>46242.458333333336</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C140" s="7">
+        <v>46243.583333333336</v>
+      </c>
+      <c r="D140" s="7">
+        <v>46243.645833333336</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C141" s="7">
+        <v>46249.395833333336</v>
+      </c>
+      <c r="D141" s="7">
+        <v>46249.458333333336</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C142" s="7">
+        <v>46250.583333333336</v>
+      </c>
+      <c r="D142" s="7">
+        <v>46250.645833333336</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" s="7">
+        <v>46256.395833333336</v>
+      </c>
+      <c r="D143" s="7">
+        <v>46256.458333333336</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C144" s="7">
+        <v>46257.625</v>
+      </c>
+      <c r="D144" s="7">
+        <v>46257.666666666664</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C145" s="7">
+        <v>46263.395833333336</v>
+      </c>
+      <c r="D145" s="7">
+        <v>46263.4375</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C146" s="7">
+        <v>46263.458333333336</v>
+      </c>
+      <c r="D146" s="7">
+        <v>46263.5</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="147" ht="15.75" customHeight="1"/>
     <row r="148" ht="15.75" customHeight="1"/>
     <row r="149" ht="15.75" customHeight="1"/>
@@ -9800,7 +10336,6 @@
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -9835,10 +10370,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C2" s="4">
         <v>46259.6666666667</v>

--- a/events.xlsx
+++ b/events.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="b8yL2kWxQclk0lTATQPPImx8IuoRrNodS6HkMoOKXP4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="BpyKi5R8V9D44cznRcqImVZeYFV5lraPojAzLcUp6f8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="63">
   <si>
     <t>title</t>
   </si>
@@ -48,7 +48,13 @@
 </t>
   </si>
   <si>
+    <t>夏祭り</t>
+  </si>
+  <si>
     <t>空手稽古</t>
+  </si>
+  <si>
+    <t>小学校</t>
   </si>
   <si>
     <t>南中山市民センター 体育館</t>
@@ -180,10 +186,28 @@
     <t>夏の体験会</t>
   </si>
   <si>
-    <t>夏祭り</t>
+    <t>八本松市民センター 和室2</t>
   </si>
   <si>
-    <t>小学校</t>
+    <t>七郷市民センター 第1＋2研修室</t>
+  </si>
+  <si>
+    <t>午後のステージ参加者発表練習のみ（通常稽古なし）</t>
+  </si>
+  <si>
+    <t>イベント</t>
+  </si>
+  <si>
+    <t>キャンドルナイト（小児がん支援イベント）・ステージ発表</t>
+  </si>
+  <si>
+    <t>プランチ仙台</t>
+  </si>
+  <si>
+    <t>合同試合</t>
+  </si>
+  <si>
+    <t>水の森市民センター</t>
   </si>
 </sst>
 </file>
@@ -7475,7 +7499,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4">
         <v>46154.7222222222</v>
@@ -7484,12 +7508,12 @@
         <v>46154.7638888889</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4">
         <v>46161.7222222222</v>
@@ -7498,12 +7522,12 @@
         <v>46161.7638888889</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4">
         <v>46168.7222222222</v>
@@ -7512,12 +7536,12 @@
         <v>46168.7638888889</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4">
         <v>46149.7083333333</v>
@@ -7526,12 +7550,12 @@
         <v>46149.75</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4">
         <v>46156.7291666666</v>
@@ -7540,12 +7564,12 @@
         <v>46156.7708333333</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="4">
         <v>46163.7083333333</v>
@@ -7554,12 +7578,12 @@
         <v>46163.75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="4">
         <v>46170.7083333333</v>
@@ -7568,12 +7592,12 @@
         <v>46170.75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4">
         <v>46155.7083333333</v>
@@ -7582,15 +7606,15 @@
         <v>46155.75</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="4">
         <v>46162.7083333333</v>
@@ -7599,15 +7623,15 @@
         <v>46162.7395833333</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" s="4">
         <v>46162.7395833333</v>
@@ -7616,12 +7640,12 @@
         <v>46162.7708333333</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="4">
         <v>46169.7083333333</v>
@@ -7630,12 +7654,12 @@
         <v>46169.75</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" s="4">
         <v>46150.6666666667</v>
@@ -7644,12 +7668,12 @@
         <v>46150.7013888889</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" s="4">
         <v>46157.6666666667</v>
@@ -7658,12 +7682,12 @@
         <v>46157.7013888889</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4">
         <v>46164.6666666667</v>
@@ -7672,12 +7696,12 @@
         <v>46164.7013888889</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" s="4">
         <v>46171.6666666667</v>
@@ -7686,15 +7710,15 @@
         <v>46171.7013888889</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C18" s="4">
         <v>46144.59375</v>
@@ -7703,15 +7727,15 @@
         <v>46144.625</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" s="4">
         <v>46144.6354166667</v>
@@ -7720,15 +7744,15 @@
         <v>46144.6666666667</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
         <v>46151.59375</v>
@@ -7737,15 +7761,15 @@
         <v>46151.625</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C21" s="4">
         <v>46151.6354166667</v>
@@ -7754,15 +7778,15 @@
         <v>46151.6666666667</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4">
         <v>46158.625</v>
@@ -7771,15 +7795,15 @@
         <v>46158.6666666667</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C23" s="4">
         <v>46172.59375</v>
@@ -7788,15 +7812,15 @@
         <v>46172.625</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4">
         <v>46172.6354166667</v>
@@ -7805,16 +7829,16 @@
         <v>46172.6666666667</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C26" s="4">
         <v>46145.4166666667</v>
@@ -7823,15 +7847,15 @@
         <v>46145.4583333333</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C27" s="4">
         <v>46152.4166666667</v>
@@ -7840,15 +7864,15 @@
         <v>46152.4583333333</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C28" s="4">
         <v>46166.4166666667</v>
@@ -7857,15 +7881,15 @@
         <v>46166.4583333333</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C29" s="4">
         <v>46173.4166666667</v>
@@ -7874,17 +7898,17 @@
         <v>46173.4583333333</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C31" s="4">
         <v>46144.3958333333</v>
@@ -7893,15 +7917,15 @@
         <v>46144.4583333333</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C32" s="4">
         <v>46145.5833333333</v>
@@ -7910,15 +7934,15 @@
         <v>46145.6458333333</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C33" s="4">
         <v>46151.3958333333</v>
@@ -7927,15 +7951,15 @@
         <v>46151.4583333333</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C34" s="4">
         <v>46158.3958333333</v>
@@ -7944,15 +7968,15 @@
         <v>46158.4583333333</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C35" s="4">
         <v>46166.5833333333</v>
@@ -7961,15 +7985,15 @@
         <v>46166.6458333333</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C36" s="4">
         <v>46173.5833333333</v>
@@ -7978,13 +8002,13 @@
         <v>46173.6458333333</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C38" s="4">
         <v>46175.7222222222</v>
@@ -7993,15 +8017,15 @@
         <v>46175.7638888889</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C39" s="4">
         <v>46182.7222222222</v>
@@ -8010,15 +8034,15 @@
         <v>46182.7638888889</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C40" s="4">
         <v>46189.7222222222</v>
@@ -8027,15 +8051,15 @@
         <v>46189.7638888889</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C41" s="4">
         <v>46196.7222222222</v>
@@ -8044,16 +8068,16 @@
         <v>46196.7638888889</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C43" s="4">
         <v>46176.7083333333</v>
@@ -8062,15 +8086,15 @@
         <v>46176.7395833333</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C44" s="4">
         <v>46176.7395833333</v>
@@ -8079,15 +8103,15 @@
         <v>46176.7708333333</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C45" s="4">
         <v>46183.7083333333</v>
@@ -8096,15 +8120,15 @@
         <v>46183.75</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C46" s="4">
         <v>46190.7083333333</v>
@@ -8113,15 +8137,15 @@
         <v>46190.7395833333</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C47" s="4">
         <v>46190.7395833333</v>
@@ -8130,15 +8154,15 @@
         <v>46190.7708333333</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C48" s="4">
         <v>46197.7083333333</v>
@@ -8147,16 +8171,16 @@
         <v>46197.75</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C50" s="4">
         <v>46184.7083333333</v>
@@ -8165,15 +8189,15 @@
         <v>46184.75</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C51" s="4">
         <v>46191.7083333333</v>
@@ -8182,15 +8206,15 @@
         <v>46191.75</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C52" s="4">
         <v>46198.7083333333</v>
@@ -8199,16 +8223,16 @@
         <v>46198.75</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C54" s="4">
         <v>46178.6666666667</v>
@@ -8217,15 +8241,15 @@
         <v>46178.7013888889</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C55" s="4">
         <v>46185.6666666667</v>
@@ -8234,15 +8258,15 @@
         <v>46185.7013888889</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C56" s="4">
         <v>46192.6666666667</v>
@@ -8251,15 +8275,15 @@
         <v>46192.7013888889</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C57" s="4">
         <v>46199.6666666667</v>
@@ -8268,16 +8292,16 @@
         <v>46199.7013888889</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1"/>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C59" s="4">
         <v>46186.625</v>
@@ -8286,15 +8310,15 @@
         <v>46186.65625</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C60" s="4">
         <v>46186.6666666667</v>
@@ -8303,15 +8327,15 @@
         <v>46186.6979166667</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C61" s="4">
         <v>46193.625</v>
@@ -8320,15 +8344,15 @@
         <v>46193.65625</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C62" s="4">
         <v>46193.6666666667</v>
@@ -8337,16 +8361,16 @@
         <v>46193.6979166667</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1"/>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C64" s="4">
         <v>46187.4166666667</v>
@@ -8355,15 +8379,15 @@
         <v>46187.4583333333</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C65" s="4">
         <v>46194.4166666667</v>
@@ -8372,16 +8396,16 @@
         <v>46194.4583333333</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C67" s="4">
         <v>46179.3958333333</v>
@@ -8390,12 +8414,12 @@
         <v>46179.4583333333</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C68" s="4">
         <v>46186.3958333333</v>
@@ -8404,12 +8428,12 @@
         <v>46186.4583333333</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C69" s="4">
         <v>46193.3958333333</v>
@@ -8418,15 +8442,15 @@
         <v>46193.4583333333</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C70" s="4">
         <v>46194.5833333333</v>
@@ -8435,12 +8459,12 @@
         <v>46194.6458333333</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C71" s="4">
         <v>46200.3958333333</v>
@@ -8449,12 +8473,12 @@
         <v>46200.4583333333</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C72" s="4">
         <v>46201.5833333333</v>
@@ -8463,16 +8487,16 @@
         <v>46201.6666666667</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C74" s="7">
         <v>46210.72222222222</v>
@@ -8481,15 +8505,15 @@
         <v>46210.76388888889</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C75" s="7">
         <v>46217.72222222222</v>
@@ -8498,15 +8522,15 @@
         <v>46217.76388888889</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C76" s="7">
         <v>46231.72222222222</v>
@@ -8515,16 +8539,16 @@
         <v>46231.76388888889</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C78" s="7">
         <v>46205.708333333336</v>
@@ -8533,15 +8557,15 @@
         <v>46205.75</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C79" s="7">
         <v>46219.708333333336</v>
@@ -8550,15 +8574,15 @@
         <v>46219.75</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C80" s="7">
         <v>46226.708333333336</v>
@@ -8567,16 +8591,16 @@
         <v>46226.75</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C82" s="7">
         <v>46211.708333333336</v>
@@ -8585,15 +8609,15 @@
         <v>46211.739583333336</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C83" s="7">
         <v>46211.739583333336</v>
@@ -8602,15 +8626,15 @@
         <v>46211.770833333336</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C84" s="7">
         <v>46218.708333333336</v>
@@ -8619,15 +8643,15 @@
         <v>46218.75</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C85" s="7">
         <v>46225.708333333336</v>
@@ -8636,15 +8660,15 @@
         <v>46225.739583333336</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C86" s="7">
         <v>46225.739583333336</v>
@@ -8653,16 +8677,16 @@
         <v>46225.770833333336</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1"/>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C88" s="7">
         <v>46206.666666666664</v>
@@ -8671,15 +8695,15 @@
         <v>46206.70138888889</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C89" s="7">
         <v>46213.666666666664</v>
@@ -8688,15 +8712,15 @@
         <v>46213.70138888889</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C90" s="7">
         <v>46220.666666666664</v>
@@ -8705,15 +8729,15 @@
         <v>46220.70138888889</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C91" s="7">
         <v>46227.666666666664</v>
@@ -8722,16 +8746,16 @@
         <v>46227.70138888889</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1"/>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C93" s="7">
         <v>46207.625</v>
@@ -8740,15 +8764,15 @@
         <v>46207.65625</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C94" s="7">
         <v>46207.666666666664</v>
@@ -8757,15 +8781,15 @@
         <v>46207.697916666664</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C95" s="7">
         <v>46214.625</v>
@@ -8774,15 +8798,15 @@
         <v>46214.65625</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C96" s="7">
         <v>46214.666666666664</v>
@@ -8791,16 +8815,16 @@
         <v>46214.697916666664</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C98" s="7">
         <v>46208.416666666664</v>
@@ -8809,15 +8833,15 @@
         <v>46208.458333333336</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C99" s="7">
         <v>46215.416666666664</v>
@@ -8826,16 +8850,16 @@
         <v>46215.458333333336</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1"/>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C101" s="7">
         <v>46207.395833333336</v>
@@ -8844,15 +8868,15 @@
         <v>46207.458333333336</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C102" s="7">
         <v>46208.583333333336</v>
@@ -8861,15 +8885,15 @@
         <v>46208.645833333336</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C103" s="7">
         <v>46214.395833333336</v>
@@ -8878,15 +8902,15 @@
         <v>46214.458333333336</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C104" s="7">
         <v>46215.583333333336</v>
@@ -8895,16 +8919,16 @@
         <v>46215.645833333336</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1"/>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C106" s="7">
         <v>46221.0</v>
@@ -8913,15 +8937,15 @@
         <v>46222.99930555555</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C107" s="7">
         <v>46228.0</v>
@@ -8930,16 +8954,16 @@
         <v>46229.99930555555</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C109" s="7">
         <v>46238.72222222222</v>
@@ -8948,15 +8972,15 @@
         <v>46238.76388888889</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C110" s="7">
         <v>46252.72222222222</v>
@@ -8965,15 +8989,15 @@
         <v>46252.76388888889</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C111" s="7">
         <v>46259.72222222222</v>
@@ -8982,16 +9006,16 @@
         <v>46259.76388888889</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1"/>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C113" s="7">
         <v>46239.708333333336</v>
@@ -9000,15 +9024,15 @@
         <v>46239.75</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C114" s="7">
         <v>46246.708333333336</v>
@@ -9017,15 +9041,15 @@
         <v>46246.739583333336</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C115" s="7">
         <v>46246.739583333336</v>
@@ -9034,15 +9058,15 @@
         <v>46246.770833333336</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C116" s="7">
         <v>46253.708333333336</v>
@@ -9051,15 +9075,15 @@
         <v>46253.75</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C117" s="7">
         <v>46260.708333333336</v>
@@ -9068,15 +9092,15 @@
         <v>46260.739583333336</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C118" s="7">
         <v>46260.739583333336</v>
@@ -9085,16 +9109,16 @@
         <v>46260.770833333336</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1"/>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C120" s="7">
         <v>46240.708333333336</v>
@@ -9103,15 +9127,15 @@
         <v>46240.75</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C121" s="7">
         <v>46247.708333333336</v>
@@ -9120,15 +9144,15 @@
         <v>46247.75</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C122" s="7">
         <v>46254.708333333336</v>
@@ -9137,15 +9161,15 @@
         <v>46254.75</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C123" s="7">
         <v>46261.729166666664</v>
@@ -9154,16 +9178,16 @@
         <v>46261.770833333336</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1"/>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C125" s="7">
         <v>46241.666666666664</v>
@@ -9172,15 +9196,15 @@
         <v>46241.70138888889</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C126" s="7">
         <v>46255.666666666664</v>
@@ -9189,15 +9213,15 @@
         <v>46255.70138888889</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C127" s="7">
         <v>46262.666666666664</v>
@@ -9206,16 +9230,16 @@
         <v>46262.70138888889</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C129" s="7">
         <v>46242.625</v>
@@ -9224,15 +9248,15 @@
         <v>46242.666666666664</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C130" s="7">
         <v>46249.625</v>
@@ -9241,15 +9265,15 @@
         <v>46249.65625</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C131" s="7">
         <v>46249.666666666664</v>
@@ -9258,15 +9282,15 @@
         <v>46249.697916666664</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C132" s="7">
         <v>46256.625</v>
@@ -9275,15 +9299,15 @@
         <v>46256.65625</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C133" s="7">
         <v>46256.666666666664</v>
@@ -9292,16 +9316,16 @@
         <v>46256.697916666664</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1"/>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C135" s="7">
         <v>46243.416666666664</v>
@@ -9310,15 +9334,15 @@
         <v>46243.458333333336</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C136" s="7">
         <v>46257.416666666664</v>
@@ -9327,15 +9351,15 @@
         <v>46257.458333333336</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C137" s="7">
         <v>46264.416666666664</v>
@@ -9344,16 +9368,16 @@
         <v>46264.458333333336</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1"/>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C139" s="7">
         <v>46242.395833333336</v>
@@ -9362,15 +9386,15 @@
         <v>46242.458333333336</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C140" s="7">
         <v>46243.583333333336</v>
@@ -9379,15 +9403,15 @@
         <v>46243.645833333336</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C141" s="7">
         <v>46249.395833333336</v>
@@ -9396,15 +9420,15 @@
         <v>46249.458333333336</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C142" s="7">
         <v>46250.583333333336</v>
@@ -9413,15 +9437,15 @@
         <v>46250.645833333336</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C143" s="7">
         <v>46256.395833333336</v>
@@ -9430,15 +9454,15 @@
         <v>46256.458333333336</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C144" s="7">
         <v>46257.625</v>
@@ -9447,15 +9471,15 @@
         <v>46257.666666666664</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C145" s="7">
         <v>46263.395833333336</v>
@@ -9464,15 +9488,15 @@
         <v>46263.4375</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C146" s="7">
         <v>46263.458333333336</v>
@@ -9481,42 +9505,554 @@
         <v>46263.5</v>
       </c>
       <c r="E146" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B148" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
+      <c r="C148" s="7">
+        <v>46270.625</v>
+      </c>
+      <c r="D148" s="7">
+        <v>46270.65625</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C149" s="7">
+        <v>46270.666666666664</v>
+      </c>
+      <c r="D149" s="7">
+        <v>46270.697916666664</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" s="7">
+        <v>46284.625</v>
+      </c>
+      <c r="D150" s="7">
+        <v>46284.65625</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" s="7">
+        <v>46284.666666666664</v>
+      </c>
+      <c r="D151" s="7">
+        <v>46284.697916666664</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="7">
+        <v>46291.625</v>
+      </c>
+      <c r="D152" s="7">
+        <v>46291.65625</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C153" s="7">
+        <v>46291.666666666664</v>
+      </c>
+      <c r="D153" s="7">
+        <v>46291.697916666664</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C154" s="7">
+        <v>46278.416666666664</v>
+      </c>
+      <c r="D154" s="7">
+        <v>46278.458333333336</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" s="7">
+        <v>46285.416666666664</v>
+      </c>
+      <c r="D155" s="7">
+        <v>46285.458333333336</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C156" s="7">
+        <v>46267.708333333336</v>
+      </c>
+      <c r="D156" s="7">
+        <v>46267.75</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C157" s="7">
+        <v>46274.708333333336</v>
+      </c>
+      <c r="D157" s="7">
+        <v>46274.739583333336</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C158" s="7">
+        <v>46274.739583333336</v>
+      </c>
+      <c r="D158" s="7">
+        <v>46274.770833333336</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" s="7">
+        <v>46281.708333333336</v>
+      </c>
+      <c r="D159" s="7">
+        <v>46281.75</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C160" s="7">
+        <v>46295.708333333336</v>
+      </c>
+      <c r="D160" s="7">
+        <v>46295.739583333336</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161" s="7">
+        <v>46295.739583333336</v>
+      </c>
+      <c r="D161" s="7">
+        <v>46295.770833333336</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C162" s="7">
+        <v>46268.708333333336</v>
+      </c>
+      <c r="D162" s="7">
+        <v>46268.75</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" s="7">
+        <v>46275.708333333336</v>
+      </c>
+      <c r="D163" s="7">
+        <v>46275.75</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C164" s="7">
+        <v>46282.708333333336</v>
+      </c>
+      <c r="D164" s="7">
+        <v>46282.75</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C165" s="7">
+        <v>46269.666666666664</v>
+      </c>
+      <c r="D165" s="7">
+        <v>46269.70138888889</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C166" s="7">
+        <v>46276.666666666664</v>
+      </c>
+      <c r="D166" s="7">
+        <v>46276.70138888889</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C167" s="7">
+        <v>46283.666666666664</v>
+      </c>
+      <c r="D167" s="7">
+        <v>46283.70138888889</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C168" s="7">
+        <v>46290.666666666664</v>
+      </c>
+      <c r="D168" s="7">
+        <v>46290.70138888889</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C169" s="7">
+        <v>46273.72222222222</v>
+      </c>
+      <c r="D169" s="7">
+        <v>46273.76388888889</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C170" s="7">
+        <v>46280.72222222222</v>
+      </c>
+      <c r="D170" s="7">
+        <v>46280.76388888889</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C171" s="7">
+        <v>46294.72222222222</v>
+      </c>
+      <c r="D171" s="7">
+        <v>46294.76388888889</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C172" s="7">
+        <v>46270.395833333336</v>
+      </c>
+      <c r="D172" s="7">
+        <v>46270.458333333336</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C173" s="7">
+        <v>46271.583333333336</v>
+      </c>
+      <c r="D173" s="7">
+        <v>46271.645833333336</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C174" s="7">
+        <v>46277.395833333336</v>
+      </c>
+      <c r="D174" s="7">
+        <v>46277.458333333336</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C175" s="7">
+        <v>46277.583333333336</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C176" s="7">
+        <v>46278.583333333336</v>
+      </c>
+      <c r="D176" s="7">
+        <v>46278.645833333336</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C177" s="7">
+        <v>46284.395833333336</v>
+      </c>
+      <c r="D177" s="7">
+        <v>46284.458333333336</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C178" s="7">
+        <v>46285.583333333336</v>
+      </c>
+      <c r="D178" s="7">
+        <v>46285.666666666664</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
+      <c r="A179" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C179" s="7">
+        <v>46291.395833333336</v>
+      </c>
+      <c r="D179" s="7">
+        <v>46291.458333333336</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="180" ht="15.75" customHeight="1"/>
     <row r="181" ht="15.75" customHeight="1"/>
     <row r="182" ht="15.75" customHeight="1"/>
@@ -10335,7 +10871,6 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -10370,10 +10905,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4">
         <v>46259.6666666667</v>

--- a/events.xlsx
+++ b/events.xlsx
@@ -6,19 +6,20 @@
     <sheet state="visible" name="club" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="Karate" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Choumeigaoka" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="Jr" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="FKcfSLhQzOVDda8B6jjzYznIQvDE8PTI6APxpHGKSM8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="BbDg2czUYiFOtYuVcz/rAq7E7P1xIDDvT7mlPHu0YTw="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="72">
   <si>
     <t>title</t>
   </si>
@@ -35,16 +36,16 @@
     <t>location</t>
   </si>
   <si>
+    <t>夏祭り</t>
+  </si>
+  <si>
+    <t>2学期中間考査</t>
+  </si>
+  <si>
     <t>空手稽古</t>
   </si>
   <si>
-    <t>夏祭り</t>
-  </si>
-  <si>
     <t>小学校</t>
-  </si>
-  <si>
-    <t>南中山市民センター 体育館</t>
   </si>
   <si>
     <t>部活動</t>
@@ -56,7 +57,13 @@
     <t>2026-05-20 08:00</t>
   </si>
   <si>
+    <t>南中山市民センター 体育館</t>
+  </si>
+  <si>
     <t>光のページェント点灯式</t>
+  </si>
+  <si>
+    <t>愛の鐘公園</t>
   </si>
   <si>
     <t>中山市民センター ホール</t>
@@ -66,9 +73,6 @@
   </si>
   <si>
     <t>東部市民センター 体育館</t>
-  </si>
-  <si>
-    <t>愛の鐘公園</t>
   </si>
   <si>
     <t>東部市民センター 大広間</t>
@@ -296,21 +300,21 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -328,6 +332,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -583,7 +591,7 @@
       <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="6">
         <v>46162.458333333336</v>
       </c>
       <c r="E2" s="2"/>
@@ -7531,3154 +7539,3154 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5">
         <v>46154.7222222222</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <v>46154.7638888889</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5">
         <v>46161.7222222222</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <v>46161.7638888889</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5">
         <v>46168.7222222222</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>46168.7638888889</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4">
+        <v>7</v>
+      </c>
+      <c r="C5" s="5">
         <v>46149.7083333333</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <v>46149.75</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
         <v>46156.7291666666</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <v>46156.7708333333</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="4">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5">
         <v>46163.7083333333</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <v>46163.75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="4">
+        <v>7</v>
+      </c>
+      <c r="C8" s="5">
         <v>46170.7083333333</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <v>46170.75</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5">
         <v>46155.7083333333</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <v>46155.75</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5">
+        <v>46162.7083333333</v>
+      </c>
+      <c r="D10" s="5">
+        <v>46162.7395833333</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C10" s="4">
-        <v>46162.7083333333</v>
-      </c>
-      <c r="D10" s="4">
-        <v>46162.7395833333</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="5">
+        <v>46162.7395833333</v>
+      </c>
+      <c r="D11" s="5">
+        <v>46162.7708333333</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C11" s="4">
-        <v>46162.7395833333</v>
-      </c>
-      <c r="D11" s="4">
-        <v>46162.7708333333</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="4">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5">
         <v>46169.7083333333</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <v>46169.75</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="4">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5">
         <v>46150.6666666667</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <v>46150.7013888889</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="4">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5">
         <v>46157.6666666667</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <v>46157.7013888889</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5">
         <v>46164.6666666667</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <v>46164.7013888889</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="4">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5">
         <v>46171.6666666667</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <v>46171.7013888889</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="4">
+        <v>23</v>
+      </c>
+      <c r="C18" s="5">
         <v>46144.59375</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <v>46144.625</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="5">
+        <v>46144.6354166667</v>
+      </c>
+      <c r="D19" s="5">
+        <v>46144.6666666667</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C19" s="4">
-        <v>46144.6354166667</v>
-      </c>
-      <c r="D19" s="4">
-        <v>46144.6666666667</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5">
         <v>46151.59375</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <v>46151.625</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="5">
+        <v>46151.6354166667</v>
+      </c>
+      <c r="D21" s="5">
+        <v>46151.6666666667</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C21" s="4">
-        <v>46151.6354166667</v>
-      </c>
-      <c r="D21" s="4">
-        <v>46151.6666666667</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="4">
+        <v>26</v>
+      </c>
+      <c r="C22" s="5">
         <v>46158.625</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <v>46158.6666666667</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="4">
+        <v>23</v>
+      </c>
+      <c r="C23" s="5">
         <v>46172.59375</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <v>46172.625</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="4">
+        <v>25</v>
+      </c>
+      <c r="C24" s="5">
         <v>46172.6354166667</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <v>46172.6666666667</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="4">
+        <v>27</v>
+      </c>
+      <c r="C26" s="5">
         <v>46145.4166666667</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <v>46145.4583333333</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" s="4">
+        <v>27</v>
+      </c>
+      <c r="C27" s="5">
         <v>46152.4166666667</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>46152.4583333333</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28" s="4">
+        <v>27</v>
+      </c>
+      <c r="C28" s="5">
         <v>46166.4166666667</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <v>46166.4583333333</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="4">
+        <v>27</v>
+      </c>
+      <c r="C29" s="5">
         <v>46173.4166666667</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <v>46173.4583333333</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="B31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="4">
+        <v>27</v>
+      </c>
+      <c r="C31" s="5">
         <v>46144.3958333333</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="5">
         <v>46144.4583333333</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="4">
+        <v>27</v>
+      </c>
+      <c r="C32" s="5">
         <v>46145.5833333333</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="5">
         <v>46145.6458333333</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="4">
+        <v>27</v>
+      </c>
+      <c r="C33" s="5">
         <v>46151.3958333333</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="5">
         <v>46151.4583333333</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="4">
+        <v>27</v>
+      </c>
+      <c r="C34" s="5">
         <v>46158.3958333333</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="5">
         <v>46158.4583333333</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="4">
+        <v>27</v>
+      </c>
+      <c r="C35" s="5">
         <v>46166.5833333333</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="5">
         <v>46166.6458333333</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="4">
+        <v>27</v>
+      </c>
+      <c r="C36" s="5">
         <v>46173.5833333333</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="5">
         <v>46173.6458333333</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="4">
+        <v>7</v>
+      </c>
+      <c r="C38" s="5">
         <v>46175.7222222222</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="5">
         <v>46175.7638888889</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="4">
+        <v>27</v>
+      </c>
+      <c r="C39" s="5">
         <v>46182.7222222222</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="5">
         <v>46182.7638888889</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="4">
+        <v>27</v>
+      </c>
+      <c r="C40" s="5">
         <v>46189.7222222222</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="5">
         <v>46189.7638888889</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C41" s="4">
+        <v>27</v>
+      </c>
+      <c r="C41" s="5">
         <v>46196.7222222222</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="5">
         <v>46196.7638888889</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="4">
+        <v>23</v>
+      </c>
+      <c r="C43" s="5">
         <v>46176.7083333333</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="5">
         <v>46176.7395833333</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="4">
+        <v>25</v>
+      </c>
+      <c r="C44" s="5">
         <v>46176.7395833333</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="5">
         <v>46176.7708333333</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" s="4">
+        <v>26</v>
+      </c>
+      <c r="C45" s="5">
         <v>46183.7083333333</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="5">
         <v>46183.75</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="4">
+        <v>23</v>
+      </c>
+      <c r="C46" s="5">
         <v>46190.7083333333</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="5">
         <v>46190.7395833333</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="4">
+        <v>25</v>
+      </c>
+      <c r="C47" s="5">
         <v>46190.7395833333</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="5">
         <v>46190.7708333333</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C48" s="4">
+        <v>26</v>
+      </c>
+      <c r="C48" s="5">
         <v>46197.7083333333</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="5">
         <v>46197.75</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C50" s="4">
+        <v>27</v>
+      </c>
+      <c r="C50" s="5">
         <v>46184.7083333333</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="5">
         <v>46184.75</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" s="4">
+        <v>27</v>
+      </c>
+      <c r="C51" s="5">
         <v>46191.7083333333</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="5">
         <v>46191.75</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C52" s="4">
+        <v>27</v>
+      </c>
+      <c r="C52" s="5">
         <v>46198.7083333333</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="5">
         <v>46198.75</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1"/>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C54" s="4">
+        <v>27</v>
+      </c>
+      <c r="C54" s="5">
         <v>46178.6666666667</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="5">
         <v>46178.7013888889</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55" s="4">
+        <v>27</v>
+      </c>
+      <c r="C55" s="5">
         <v>46185.6666666667</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="5">
         <v>46185.7013888889</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C56" s="4">
+        <v>27</v>
+      </c>
+      <c r="C56" s="5">
         <v>46192.6666666667</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="5">
         <v>46192.7013888889</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C57" s="4">
+        <v>27</v>
+      </c>
+      <c r="C57" s="5">
         <v>46199.6666666667</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="5">
         <v>46199.7013888889</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1"/>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C59" s="4">
+        <v>23</v>
+      </c>
+      <c r="C59" s="5">
         <v>46186.625</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="5">
         <v>46186.65625</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46186.6666666667</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46186.6979166667</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C60" s="4">
-        <v>46186.6666666667</v>
-      </c>
-      <c r="D60" s="4">
-        <v>46186.6979166667</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C61" s="4">
+        <v>23</v>
+      </c>
+      <c r="C61" s="5">
         <v>46193.625</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="5">
         <v>46193.65625</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="5">
+        <v>46193.6666666667</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46193.6979166667</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C62" s="4">
-        <v>46193.6666666667</v>
-      </c>
-      <c r="D62" s="4">
-        <v>46193.6979166667</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1"/>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C64" s="4">
+        <v>27</v>
+      </c>
+      <c r="C64" s="5">
         <v>46187.4166666667</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="5">
         <v>46187.4583333333</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C65" s="4">
+        <v>27</v>
+      </c>
+      <c r="C65" s="5">
         <v>46194.4166666667</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="5">
         <v>46194.4583333333</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C67" s="4">
+        <v>33</v>
+      </c>
+      <c r="C67" s="5">
         <v>46179.3958333333</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="5">
         <v>46179.4583333333</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C68" s="4">
+        <v>7</v>
+      </c>
+      <c r="C68" s="5">
         <v>46186.3958333333</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="5">
         <v>46186.4583333333</v>
       </c>
-      <c r="E68" s="8" t="s">
-        <v>29</v>
+      <c r="E68" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="4">
+        <v>7</v>
+      </c>
+      <c r="C69" s="5">
         <v>46193.3958333333</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="5">
         <v>46193.4583333333</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>34</v>
+      <c r="E69" s="9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C70" s="4">
+        <v>36</v>
+      </c>
+      <c r="C70" s="5">
         <v>46194.5833333333</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="5">
         <v>46194.6458333333</v>
       </c>
-      <c r="E70" s="8" t="s">
-        <v>31</v>
+      <c r="E70" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C71" s="4">
+        <v>7</v>
+      </c>
+      <c r="C71" s="5">
         <v>46200.3958333333</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="5">
         <v>46200.4583333333</v>
       </c>
-      <c r="E71" s="8" t="s">
-        <v>29</v>
+      <c r="E71" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C72" s="4">
+        <v>7</v>
+      </c>
+      <c r="C72" s="5">
         <v>46201.5833333333</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="5">
         <v>46201.6666666667</v>
       </c>
-      <c r="E72" s="8" t="s">
-        <v>31</v>
+      <c r="E72" s="9" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C74" s="9">
+      <c r="A74" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" s="10">
         <v>46210.72222222222</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="10">
         <v>46210.76388888889</v>
       </c>
-      <c r="E74" s="8" t="s">
-        <v>8</v>
+      <c r="E74" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C75" s="9">
+      <c r="A75" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" s="10">
         <v>46217.72222222222</v>
       </c>
-      <c r="D75" s="9">
+      <c r="D75" s="10">
         <v>46217.76388888889</v>
       </c>
-      <c r="E75" s="8" t="s">
-        <v>8</v>
+      <c r="E75" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" s="9">
+      <c r="A76" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" s="10">
         <v>46231.72222222222</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="10">
         <v>46231.76388888889</v>
       </c>
-      <c r="E76" s="8" t="s">
-        <v>8</v>
+      <c r="E76" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1"/>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" s="9">
+      <c r="A78" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" s="10">
         <v>46205.708333333336</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="10">
         <v>46205.75</v>
       </c>
-      <c r="E78" s="8" t="s">
-        <v>14</v>
+      <c r="E78" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C79" s="9">
+      <c r="A79" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" s="10">
         <v>46219.708333333336</v>
       </c>
-      <c r="D79" s="9">
+      <c r="D79" s="10">
         <v>46219.75</v>
       </c>
-      <c r="E79" s="8" t="s">
-        <v>17</v>
+      <c r="E79" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C80" s="9">
+      <c r="A80" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80" s="10">
         <v>46226.708333333336</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="10">
         <v>46226.75</v>
       </c>
-      <c r="E80" s="8" t="s">
-        <v>17</v>
+      <c r="E80" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C82" s="9">
+      <c r="A82" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" s="10">
         <v>46211.708333333336</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="10">
         <v>46211.739583333336</v>
       </c>
-      <c r="E82" s="8" t="s">
-        <v>18</v>
+      <c r="E82" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83" s="10">
+        <v>46211.739583333336</v>
+      </c>
+      <c r="D83" s="10">
+        <v>46211.770833333336</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="10">
+        <v>46218.708333333336</v>
+      </c>
+      <c r="D84" s="10">
+        <v>46218.75</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B83" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C83" s="9">
-        <v>46211.739583333336</v>
-      </c>
-      <c r="D83" s="9">
-        <v>46211.770833333336</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="8" t="s">
+      <c r="B85" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" s="10">
+        <v>46225.708333333336</v>
+      </c>
+      <c r="D85" s="10">
+        <v>46225.739583333336</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B84" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C84" s="9">
-        <v>46218.708333333336</v>
-      </c>
-      <c r="D84" s="9">
-        <v>46218.75</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C85" s="9">
-        <v>46225.708333333336</v>
-      </c>
-      <c r="D85" s="9">
+      <c r="B86" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" s="10">
         <v>46225.739583333336</v>
       </c>
-      <c r="E85" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C86" s="9">
-        <v>46225.739583333336</v>
-      </c>
-      <c r="D86" s="9">
+      <c r="D86" s="10">
         <v>46225.770833333336</v>
       </c>
-      <c r="E86" s="8" t="s">
-        <v>18</v>
+      <c r="E86" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1"/>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C88" s="9">
+      <c r="A88" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" s="10">
         <v>46206.666666666664</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="10">
         <v>46206.70138888889</v>
       </c>
-      <c r="E88" s="8" t="s">
-        <v>21</v>
+      <c r="E88" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C89" s="9">
+      <c r="A89" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="10">
         <v>46213.666666666664</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="10">
         <v>46213.70138888889</v>
       </c>
-      <c r="E89" s="8" t="s">
-        <v>21</v>
+      <c r="E89" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C90" s="9">
+      <c r="A90" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90" s="10">
         <v>46220.666666666664</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="10">
         <v>46220.70138888889</v>
       </c>
-      <c r="E90" s="8" t="s">
-        <v>21</v>
+      <c r="E90" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C91" s="9">
+      <c r="A91" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" s="10">
         <v>46227.666666666664</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="10">
         <v>46227.70138888889</v>
       </c>
-      <c r="E91" s="8" t="s">
-        <v>21</v>
+      <c r="E91" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1"/>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C93" s="9">
+      <c r="A93" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" s="10">
         <v>46207.625</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="10">
         <v>46207.65625</v>
       </c>
-      <c r="E93" s="8" t="s">
-        <v>18</v>
+      <c r="E93" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="10">
+        <v>46207.666666666664</v>
+      </c>
+      <c r="D94" s="10">
+        <v>46207.697916666664</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B94" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C94" s="9">
-        <v>46207.666666666664</v>
-      </c>
-      <c r="D94" s="9">
-        <v>46207.697916666664</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C95" s="9">
+      <c r="B95" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="10">
         <v>46214.625</v>
       </c>
-      <c r="D95" s="9">
+      <c r="D95" s="10">
         <v>46214.65625</v>
       </c>
-      <c r="E95" s="8" t="s">
-        <v>23</v>
+      <c r="E95" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C96" s="9">
+      <c r="A96" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" s="10">
         <v>46214.666666666664</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="10">
         <v>46214.697916666664</v>
       </c>
-      <c r="E96" s="8" t="s">
-        <v>23</v>
+      <c r="E96" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1"/>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C98" s="9">
+      <c r="A98" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="10">
         <v>46208.416666666664</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="10">
         <v>46208.458333333336</v>
       </c>
-      <c r="E98" s="8" t="s">
-        <v>27</v>
+      <c r="E98" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C99" s="9">
+      <c r="A99" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99" s="10">
         <v>46215.416666666664</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="10">
         <v>46215.458333333336</v>
       </c>
-      <c r="E99" s="8" t="s">
-        <v>27</v>
+      <c r="E99" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1"/>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C101" s="9">
+      <c r="A101" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="10">
         <v>46207.395833333336</v>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="10">
         <v>46207.458333333336</v>
       </c>
-      <c r="E101" s="8" t="s">
-        <v>28</v>
+      <c r="E101" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C102" s="9">
+      <c r="A102" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102" s="10">
         <v>46208.583333333336</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="10">
         <v>46208.645833333336</v>
       </c>
-      <c r="E102" s="8" t="s">
-        <v>28</v>
+      <c r="E102" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B103" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C103" s="9">
+      <c r="A103" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C103" s="10">
         <v>46214.395833333336</v>
       </c>
-      <c r="D103" s="9">
+      <c r="D103" s="10">
         <v>46214.458333333336</v>
       </c>
-      <c r="E103" s="8" t="s">
-        <v>42</v>
+      <c r="E103" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C104" s="9">
+      <c r="A104" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104" s="10">
         <v>46215.583333333336</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="10">
         <v>46215.645833333336</v>
       </c>
-      <c r="E104" s="8" t="s">
-        <v>30</v>
+      <c r="E104" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1"/>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B106" s="8" t="s">
+      <c r="A106" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C106" s="9">
+      <c r="B106" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C106" s="10">
         <v>46221.0</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="10">
         <v>46222.99930555555</v>
       </c>
-      <c r="E106" s="8" t="s">
-        <v>45</v>
+      <c r="E106" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B107" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C107" s="9">
+      <c r="A107" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C107" s="10">
         <v>46228.0</v>
       </c>
-      <c r="D107" s="9">
+      <c r="D107" s="10">
         <v>46229.99930555555</v>
       </c>
-      <c r="E107" s="8" t="s">
-        <v>47</v>
+      <c r="E107" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B109" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C109" s="9">
+      <c r="A109" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109" s="10">
         <v>46238.72222222222</v>
       </c>
-      <c r="D109" s="9">
+      <c r="D109" s="10">
         <v>46238.76388888889</v>
       </c>
-      <c r="E109" s="8" t="s">
-        <v>13</v>
+      <c r="E109" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C110" s="9">
+      <c r="A110" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C110" s="10">
         <v>46252.72222222222</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="10">
         <v>46252.76388888889</v>
       </c>
-      <c r="E110" s="8" t="s">
-        <v>8</v>
+      <c r="E110" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B111" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C111" s="9">
+      <c r="A111" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111" s="10">
         <v>46259.72222222222</v>
       </c>
-      <c r="D111" s="9">
+      <c r="D111" s="10">
         <v>46259.76388888889</v>
       </c>
-      <c r="E111" s="8" t="s">
-        <v>8</v>
+      <c r="E111" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1"/>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C113" s="10">
+        <v>46239.708333333336</v>
+      </c>
+      <c r="D113" s="10">
+        <v>46239.75</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C114" s="10">
+        <v>46246.708333333336</v>
+      </c>
+      <c r="D114" s="10">
+        <v>46246.739583333336</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B113" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C113" s="9">
-        <v>46239.708333333336</v>
-      </c>
-      <c r="D113" s="9">
-        <v>46239.75</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B114" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C114" s="9">
-        <v>46246.708333333336</v>
-      </c>
-      <c r="D114" s="9">
+      <c r="B115" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115" s="10">
         <v>46246.739583333336</v>
       </c>
-      <c r="E114" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="8" t="s">
+      <c r="D115" s="10">
+        <v>46246.770833333336</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116" s="10">
+        <v>46253.708333333336</v>
+      </c>
+      <c r="D116" s="10">
+        <v>46253.75</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B115" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C115" s="9">
-        <v>46246.739583333336</v>
-      </c>
-      <c r="D115" s="9">
-        <v>46246.770833333336</v>
-      </c>
-      <c r="E115" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="8" t="s">
+      <c r="B117" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C117" s="10">
+        <v>46260.708333333336</v>
+      </c>
+      <c r="D117" s="10">
+        <v>46260.739583333336</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B116" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C116" s="9">
-        <v>46253.708333333336</v>
-      </c>
-      <c r="D116" s="9">
-        <v>46253.75</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C117" s="9">
-        <v>46260.708333333336</v>
-      </c>
-      <c r="D117" s="9">
+      <c r="B118" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C118" s="10">
         <v>46260.739583333336</v>
       </c>
-      <c r="E117" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C118" s="9">
-        <v>46260.739583333336</v>
-      </c>
-      <c r="D118" s="9">
+      <c r="D118" s="10">
         <v>46260.770833333336</v>
       </c>
-      <c r="E118" s="8" t="s">
-        <v>18</v>
+      <c r="E118" s="9" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1"/>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C120" s="9">
+      <c r="A120" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C120" s="10">
         <v>46240.708333333336</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="10">
         <v>46240.75</v>
       </c>
-      <c r="E120" s="8" t="s">
-        <v>14</v>
+      <c r="E120" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C121" s="9">
+      <c r="A121" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121" s="10">
         <v>46247.708333333336</v>
       </c>
-      <c r="D121" s="9">
+      <c r="D121" s="10">
         <v>46247.75</v>
       </c>
-      <c r="E121" s="8" t="s">
+      <c r="E121" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C122" s="10">
+        <v>46254.708333333336</v>
+      </c>
+      <c r="D122" s="10">
+        <v>46254.75</v>
+      </c>
+      <c r="E122" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C123" s="10">
+        <v>46261.729166666664</v>
+      </c>
+      <c r="D123" s="10">
+        <v>46261.770833333336</v>
+      </c>
+      <c r="E123" s="9" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B122" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C122" s="9">
-        <v>46254.708333333336</v>
-      </c>
-      <c r="D122" s="9">
-        <v>46254.75</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B123" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C123" s="9">
-        <v>46261.729166666664</v>
-      </c>
-      <c r="D123" s="9">
-        <v>46261.770833333336</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1"/>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B125" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C125" s="9">
+      <c r="A125" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C125" s="10">
         <v>46241.666666666664</v>
       </c>
-      <c r="D125" s="9">
+      <c r="D125" s="10">
         <v>46241.70138888889</v>
       </c>
-      <c r="E125" s="8" t="s">
-        <v>21</v>
+      <c r="E125" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B126" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C126" s="9">
+      <c r="A126" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C126" s="10">
         <v>46255.666666666664</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="10">
         <v>46255.70138888889</v>
       </c>
-      <c r="E126" s="8" t="s">
-        <v>21</v>
+      <c r="E126" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B127" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C127" s="9">
+      <c r="A127" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C127" s="10">
         <v>46262.666666666664</v>
       </c>
-      <c r="D127" s="9">
+      <c r="D127" s="10">
         <v>46262.70138888889</v>
       </c>
-      <c r="E127" s="8" t="s">
-        <v>21</v>
+      <c r="E127" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B129" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C129" s="9">
+      <c r="A129" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C129" s="10">
         <v>46242.625</v>
       </c>
-      <c r="D129" s="9">
+      <c r="D129" s="10">
         <v>46242.666666666664</v>
       </c>
-      <c r="E129" s="8" t="s">
-        <v>48</v>
+      <c r="E129" s="9" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C130" s="9">
+      <c r="A130" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" s="10">
         <v>46249.625</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="10">
         <v>46249.65625</v>
       </c>
-      <c r="E130" s="8" t="s">
-        <v>23</v>
+      <c r="E130" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C131" s="10">
+        <v>46249.666666666664</v>
+      </c>
+      <c r="D131" s="10">
+        <v>46249.697916666664</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B131" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C131" s="9">
-        <v>46249.666666666664</v>
-      </c>
-      <c r="D131" s="9">
-        <v>46249.697916666664</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C132" s="9">
+      <c r="B132" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C132" s="10">
         <v>46256.625</v>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="10">
         <v>46256.65625</v>
       </c>
-      <c r="E132" s="8" t="s">
-        <v>23</v>
+      <c r="E132" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B133" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C133" s="9">
+      <c r="A133" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C133" s="10">
         <v>46256.666666666664</v>
       </c>
-      <c r="D133" s="9">
+      <c r="D133" s="10">
         <v>46256.697916666664</v>
       </c>
-      <c r="E133" s="8" t="s">
-        <v>23</v>
+      <c r="E133" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1"/>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B135" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C135" s="9">
+      <c r="A135" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C135" s="10">
         <v>46243.416666666664</v>
       </c>
-      <c r="D135" s="9">
+      <c r="D135" s="10">
         <v>46243.458333333336</v>
       </c>
-      <c r="E135" s="8" t="s">
-        <v>27</v>
+      <c r="E135" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C136" s="9">
+      <c r="A136" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C136" s="10">
         <v>46257.416666666664</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="10">
         <v>46257.458333333336</v>
       </c>
-      <c r="E136" s="8" t="s">
-        <v>49</v>
+      <c r="E136" s="9" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C137" s="9">
+      <c r="A137" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" s="10">
         <v>46264.416666666664</v>
       </c>
-      <c r="D137" s="9">
+      <c r="D137" s="10">
         <v>46264.458333333336</v>
       </c>
-      <c r="E137" s="8" t="s">
-        <v>27</v>
+      <c r="E137" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1"/>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B139" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C139" s="9">
+      <c r="A139" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C139" s="10">
         <v>46242.395833333336</v>
       </c>
-      <c r="D139" s="9">
+      <c r="D139" s="10">
         <v>46242.458333333336</v>
       </c>
-      <c r="E139" s="8" t="s">
-        <v>50</v>
+      <c r="E139" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B140" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C140" s="9">
+      <c r="A140" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C140" s="10">
         <v>46243.583333333336</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="10">
         <v>46243.645833333336</v>
       </c>
-      <c r="E140" s="8" t="s">
-        <v>30</v>
+      <c r="E140" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C141" s="9">
+      <c r="A141" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C141" s="10">
         <v>46249.395833333336</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D141" s="10">
         <v>46249.458333333336</v>
       </c>
-      <c r="E141" s="8" t="s">
+      <c r="E141" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C142" s="10">
+        <v>46250.583333333336</v>
+      </c>
+      <c r="D142" s="10">
+        <v>46250.645833333336</v>
+      </c>
+      <c r="E142" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C143" s="10">
+        <v>46256.395833333336</v>
+      </c>
+      <c r="D143" s="10">
+        <v>46256.458333333336</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C144" s="10">
+        <v>46257.625</v>
+      </c>
+      <c r="D144" s="10">
+        <v>46257.666666666664</v>
+      </c>
+      <c r="E144" s="9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C142" s="9">
-        <v>46250.583333333336</v>
-      </c>
-      <c r="D142" s="9">
-        <v>46250.645833333336</v>
-      </c>
-      <c r="E142" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B143" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C143" s="9">
-        <v>46256.395833333336</v>
-      </c>
-      <c r="D143" s="9">
-        <v>46256.458333333336</v>
-      </c>
-      <c r="E143" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B144" s="8" t="s">
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C145" s="10">
+        <v>46263.395833333336</v>
+      </c>
+      <c r="D145" s="10">
+        <v>46263.4375</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C144" s="9">
-        <v>46257.625</v>
-      </c>
-      <c r="D144" s="9">
-        <v>46257.666666666664</v>
-      </c>
-      <c r="E144" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B145" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C145" s="9">
-        <v>46263.395833333336</v>
-      </c>
-      <c r="D145" s="9">
-        <v>46263.4375</v>
-      </c>
-      <c r="E145" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B146" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C146" s="9">
+      <c r="B146" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C146" s="10">
         <v>46263.458333333336</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="10">
         <v>46263.5</v>
       </c>
-      <c r="E146" s="8" t="s">
-        <v>28</v>
+      <c r="E146" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1"/>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="8" t="s">
+      <c r="A148" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C148" s="10">
+        <v>46270.625</v>
+      </c>
+      <c r="D148" s="10">
+        <v>46270.65625</v>
+      </c>
+      <c r="E148" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C149" s="10">
+        <v>46270.666666666664</v>
+      </c>
+      <c r="D149" s="10">
+        <v>46270.697916666664</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C150" s="10">
+        <v>46284.625</v>
+      </c>
+      <c r="D150" s="10">
+        <v>46284.65625</v>
+      </c>
+      <c r="E150" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C151" s="10">
+        <v>46284.666666666664</v>
+      </c>
+      <c r="D151" s="10">
+        <v>46284.697916666664</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C152" s="10">
+        <v>46291.625</v>
+      </c>
+      <c r="D152" s="10">
+        <v>46291.65625</v>
+      </c>
+      <c r="E152" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C153" s="10">
+        <v>46291.666666666664</v>
+      </c>
+      <c r="D153" s="10">
+        <v>46291.697916666664</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B148" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C148" s="9">
-        <v>46270.625</v>
-      </c>
-      <c r="D148" s="9">
-        <v>46270.65625</v>
-      </c>
-      <c r="E148" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="8" t="s">
+      <c r="B154" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C154" s="10">
+        <v>46278.416666666664</v>
+      </c>
+      <c r="D154" s="10">
+        <v>46278.458333333336</v>
+      </c>
+      <c r="E154" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C155" s="10">
+        <v>46285.416666666664</v>
+      </c>
+      <c r="D155" s="10">
+        <v>46285.458333333336</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C156" s="10">
+        <v>46267.708333333336</v>
+      </c>
+      <c r="D156" s="10">
+        <v>46267.75</v>
+      </c>
+      <c r="E156" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B149" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C149" s="9">
-        <v>46270.666666666664</v>
-      </c>
-      <c r="D149" s="9">
-        <v>46270.697916666664</v>
-      </c>
-      <c r="E149" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="8" t="s">
+      <c r="B157" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C157" s="10">
+        <v>46274.708333333336</v>
+      </c>
+      <c r="D157" s="10">
+        <v>46274.739583333336</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C158" s="10">
+        <v>46274.739583333336</v>
+      </c>
+      <c r="D158" s="10">
+        <v>46274.770833333336</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C159" s="10">
+        <v>46281.708333333336</v>
+      </c>
+      <c r="D159" s="10">
+        <v>46281.75</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C160" s="10">
+        <v>46295.708333333336</v>
+      </c>
+      <c r="D160" s="10">
+        <v>46295.739583333336</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C161" s="10">
+        <v>46295.739583333336</v>
+      </c>
+      <c r="D161" s="10">
+        <v>46295.770833333336</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B150" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C150" s="9">
-        <v>46284.625</v>
-      </c>
-      <c r="D150" s="9">
-        <v>46284.65625</v>
-      </c>
-      <c r="E150" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B151" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C151" s="9">
-        <v>46284.666666666664</v>
-      </c>
-      <c r="D151" s="9">
-        <v>46284.697916666664</v>
-      </c>
-      <c r="E151" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="8" t="s">
+      <c r="B162" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C162" s="10">
+        <v>46268.708333333336</v>
+      </c>
+      <c r="D162" s="10">
+        <v>46268.75</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B152" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C152" s="9">
-        <v>46291.625</v>
-      </c>
-      <c r="D152" s="9">
-        <v>46291.65625</v>
-      </c>
-      <c r="E152" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B153" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C153" s="9">
-        <v>46291.666666666664</v>
-      </c>
-      <c r="D153" s="9">
-        <v>46291.697916666664</v>
-      </c>
-      <c r="E153" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B154" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C154" s="9">
-        <v>46278.416666666664</v>
-      </c>
-      <c r="D154" s="9">
-        <v>46278.458333333336</v>
-      </c>
-      <c r="E154" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B155" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C155" s="9">
-        <v>46285.416666666664</v>
-      </c>
-      <c r="D155" s="9">
-        <v>46285.458333333336</v>
-      </c>
-      <c r="E155" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B156" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C156" s="9">
-        <v>46267.708333333336</v>
-      </c>
-      <c r="D156" s="9">
-        <v>46267.75</v>
-      </c>
-      <c r="E156" s="8" t="s">
+      <c r="B163" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C163" s="10">
+        <v>46275.708333333336</v>
+      </c>
+      <c r="D163" s="10">
+        <v>46275.75</v>
+      </c>
+      <c r="E163" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="8" t="s">
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B157" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C157" s="9">
-        <v>46274.708333333336</v>
-      </c>
-      <c r="D157" s="9">
-        <v>46274.739583333336</v>
-      </c>
-      <c r="E157" s="8" t="s">
+      <c r="B164" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C164" s="10">
+        <v>46282.708333333336</v>
+      </c>
+      <c r="D164" s="10">
+        <v>46282.75</v>
+      </c>
+      <c r="E164" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B158" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C158" s="9">
-        <v>46274.739583333336</v>
-      </c>
-      <c r="D158" s="9">
-        <v>46274.770833333336</v>
-      </c>
-      <c r="E158" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B159" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C159" s="9">
-        <v>46281.708333333336</v>
-      </c>
-      <c r="D159" s="9">
-        <v>46281.75</v>
-      </c>
-      <c r="E159" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="8" t="s">
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B160" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C160" s="9">
-        <v>46295.708333333336</v>
-      </c>
-      <c r="D160" s="9">
-        <v>46295.739583333336</v>
-      </c>
-      <c r="E160" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B161" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C161" s="9">
-        <v>46295.739583333336</v>
-      </c>
-      <c r="D161" s="9">
-        <v>46295.770833333336</v>
-      </c>
-      <c r="E161" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B162" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C162" s="9">
-        <v>46268.708333333336</v>
-      </c>
-      <c r="D162" s="9">
-        <v>46268.75</v>
-      </c>
-      <c r="E162" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B163" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C163" s="9">
-        <v>46275.708333333336</v>
-      </c>
-      <c r="D163" s="9">
-        <v>46275.75</v>
-      </c>
-      <c r="E163" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B164" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C164" s="9">
-        <v>46282.708333333336</v>
-      </c>
-      <c r="D164" s="9">
-        <v>46282.75</v>
-      </c>
-      <c r="E164" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B165" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C165" s="9">
+      <c r="B165" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C165" s="10">
         <v>46269.666666666664</v>
       </c>
-      <c r="D165" s="9">
+      <c r="D165" s="10">
         <v>46269.70138888889</v>
       </c>
-      <c r="E165" s="8" t="s">
-        <v>21</v>
+      <c r="E165" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B166" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C166" s="9">
+      <c r="A166" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C166" s="10">
         <v>46276.666666666664</v>
       </c>
-      <c r="D166" s="9">
+      <c r="D166" s="10">
         <v>46276.70138888889</v>
       </c>
-      <c r="E166" s="8" t="s">
-        <v>21</v>
+      <c r="E166" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B167" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C167" s="9">
+      <c r="A167" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C167" s="10">
         <v>46283.666666666664</v>
       </c>
-      <c r="D167" s="9">
+      <c r="D167" s="10">
         <v>46283.70138888889</v>
       </c>
-      <c r="E167" s="8" t="s">
-        <v>21</v>
+      <c r="E167" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B168" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C168" s="9">
+      <c r="A168" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C168" s="10">
         <v>46290.666666666664</v>
       </c>
-      <c r="D168" s="9">
+      <c r="D168" s="10">
         <v>46290.70138888889</v>
       </c>
-      <c r="E168" s="8" t="s">
-        <v>21</v>
+      <c r="E168" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B169" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C169" s="9">
+      <c r="A169" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C169" s="10">
         <v>46273.72222222222</v>
       </c>
-      <c r="D169" s="9">
+      <c r="D169" s="10">
         <v>46273.76388888889</v>
       </c>
-      <c r="E169" s="8" t="s">
-        <v>8</v>
+      <c r="E169" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C170" s="9">
+      <c r="A170" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C170" s="10">
         <v>46280.72222222222</v>
       </c>
-      <c r="D170" s="9">
+      <c r="D170" s="10">
         <v>46280.76388888889</v>
       </c>
-      <c r="E170" s="8" t="s">
-        <v>8</v>
+      <c r="E170" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B171" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C171" s="9">
+      <c r="A171" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C171" s="10">
         <v>46294.72222222222</v>
       </c>
-      <c r="D171" s="9">
+      <c r="D171" s="10">
         <v>46294.76388888889</v>
       </c>
-      <c r="E171" s="8" t="s">
-        <v>13</v>
+      <c r="E171" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B172" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C172" s="9">
+      <c r="A172" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C172" s="10">
         <v>46270.395833333336</v>
       </c>
-      <c r="D172" s="9">
+      <c r="D172" s="10">
         <v>46270.458333333336</v>
       </c>
-      <c r="E172" s="8" t="s">
+      <c r="E172" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C173" s="10">
+        <v>46271.583333333336</v>
+      </c>
+      <c r="D173" s="10">
+        <v>46271.645833333336</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B174" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C174" s="10">
+        <v>46277.395833333336</v>
+      </c>
+      <c r="D174" s="10">
+        <v>46277.458333333336</v>
+      </c>
+      <c r="E174" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C173" s="9">
-        <v>46271.583333333336</v>
-      </c>
-      <c r="D173" s="9">
-        <v>46271.645833333336</v>
-      </c>
-      <c r="E173" s="8" t="s">
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C175" s="10">
+        <v>46277.583333333336</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C176" s="10">
+        <v>46278.583333333336</v>
+      </c>
+      <c r="D176" s="10">
+        <v>46278.645833333336</v>
+      </c>
+      <c r="E176" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C177" s="10">
+        <v>46284.395833333336</v>
+      </c>
+      <c r="D177" s="10">
+        <v>46284.458333333336</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C178" s="10">
+        <v>46285.583333333336</v>
+      </c>
+      <c r="D178" s="10">
+        <v>46285.666666666664</v>
+      </c>
+      <c r="E178" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B174" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C174" s="9">
-        <v>46277.395833333336</v>
-      </c>
-      <c r="D174" s="9">
-        <v>46277.458333333336</v>
-      </c>
-      <c r="E174" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B175" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C175" s="9">
-        <v>46277.583333333336</v>
-      </c>
-      <c r="D175" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E175" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B176" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C176" s="9">
-        <v>46278.583333333336</v>
-      </c>
-      <c r="D176" s="9">
-        <v>46278.645833333336</v>
-      </c>
-      <c r="E176" s="8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B177" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C177" s="9">
-        <v>46284.395833333336</v>
-      </c>
-      <c r="D177" s="9">
-        <v>46284.458333333336</v>
-      </c>
-      <c r="E177" s="8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B178" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C178" s="9">
-        <v>46285.583333333336</v>
-      </c>
-      <c r="D178" s="9">
-        <v>46285.666666666664</v>
-      </c>
-      <c r="E178" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B179" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C179" s="9">
+      <c r="A179" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C179" s="10">
         <v>46291.395833333336</v>
       </c>
-      <c r="D179" s="9">
+      <c r="D179" s="10">
         <v>46291.458333333336</v>
       </c>
-      <c r="E179" s="8" t="s">
-        <v>63</v>
+      <c r="E179" s="9" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1"/>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C181" s="10">
+      <c r="A181" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C181" s="8">
         <v>46301.72222222222</v>
       </c>
-      <c r="D181" s="10">
+      <c r="D181" s="8">
         <v>46301.76388888889</v>
       </c>
-      <c r="E181" s="6" t="s">
-        <v>8</v>
+      <c r="E181" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C182" s="10">
+      <c r="A182" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C182" s="8">
         <v>46315.72222222222</v>
       </c>
-      <c r="D182" s="10">
+      <c r="D182" s="8">
         <v>46315.76388888889</v>
       </c>
-      <c r="E182" s="6" t="s">
-        <v>13</v>
+      <c r="E182" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C183" s="10">
+      <c r="A183" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C183" s="8">
         <v>46322.72222222222</v>
       </c>
-      <c r="D183" s="10">
+      <c r="D183" s="8">
         <v>46322.76388888889</v>
       </c>
-      <c r="E183" s="6" t="s">
-        <v>64</v>
+      <c r="E183" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C184" s="10">
+      <c r="A184" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C184" s="8">
         <v>46296.708333333336</v>
       </c>
-      <c r="D184" s="10">
+      <c r="D184" s="8">
         <v>46296.75</v>
       </c>
-      <c r="E184" s="6" t="s">
-        <v>14</v>
+      <c r="E184" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C185" s="10">
+      <c r="A185" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C185" s="8">
         <v>46303.708333333336</v>
       </c>
-      <c r="D185" s="10">
+      <c r="D185" s="8">
         <v>46303.75</v>
       </c>
-      <c r="E185" s="6" t="s">
-        <v>17</v>
+      <c r="E185" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C186" s="10">
+      <c r="A186" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C186" s="8">
         <v>46310.708333333336</v>
       </c>
-      <c r="D186" s="10">
+      <c r="D186" s="8">
         <v>46310.75</v>
       </c>
-      <c r="E186" s="6" t="s">
-        <v>17</v>
+      <c r="E186" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C187" s="10">
+      <c r="A187" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C187" s="8">
         <v>46317.708333333336</v>
       </c>
-      <c r="D187" s="10">
+      <c r="D187" s="8">
         <v>46317.75</v>
       </c>
-      <c r="E187" s="6" t="s">
-        <v>17</v>
+      <c r="E187" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C188" s="8">
+        <v>46302.708333333336</v>
+      </c>
+      <c r="D188" s="8">
+        <v>46302.739583333336</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
+      <c r="A189" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C189" s="8">
+        <v>46302.739583333336</v>
+      </c>
+      <c r="D189" s="8">
+        <v>46302.770833333336</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
+      <c r="A190" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C190" s="8">
+        <v>46309.708333333336</v>
+      </c>
+      <c r="D190" s="8">
+        <v>46309.739583333336</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
+      <c r="A191" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C191" s="8">
+        <v>46309.739583333336</v>
+      </c>
+      <c r="D191" s="8">
+        <v>46309.770833333336</v>
+      </c>
+      <c r="E191" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
+      <c r="A192" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C192" s="8">
+        <v>46316.708333333336</v>
+      </c>
+      <c r="D192" s="8">
+        <v>46316.739583333336</v>
+      </c>
+      <c r="E192" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C193" s="8">
+        <v>46316.739583333336</v>
+      </c>
+      <c r="D193" s="8">
+        <v>46316.770833333336</v>
+      </c>
+      <c r="E193" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
+      <c r="A194" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C194" s="8">
+        <v>46323.708333333336</v>
+      </c>
+      <c r="D194" s="8">
+        <v>46323.739583333336</v>
+      </c>
+      <c r="E194" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
+      <c r="A195" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C195" s="8">
+        <v>46323.739583333336</v>
+      </c>
+      <c r="D195" s="8">
+        <v>46323.770833333336</v>
+      </c>
+      <c r="E195" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
+      <c r="A196" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B188" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C188" s="10">
-        <v>46302.708333333336</v>
-      </c>
-      <c r="D188" s="10">
-        <v>46302.739583333336</v>
-      </c>
-      <c r="E188" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="6" t="s">
+      <c r="B196" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C196" s="8">
+        <v>46297.666666666664</v>
+      </c>
+      <c r="D196" s="8">
+        <v>46297.70138888889</v>
+      </c>
+      <c r="E196" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
+      <c r="A197" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C197" s="8">
+        <v>46304.666666666664</v>
+      </c>
+      <c r="D197" s="8">
+        <v>46304.70138888889</v>
+      </c>
+      <c r="E197" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
+      <c r="A198" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C198" s="8">
+        <v>46311.666666666664</v>
+      </c>
+      <c r="D198" s="8">
+        <v>46311.70138888889</v>
+      </c>
+      <c r="E198" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
+      <c r="A199" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C199" s="8">
+        <v>46318.666666666664</v>
+      </c>
+      <c r="D199" s="8">
+        <v>46318.70138888889</v>
+      </c>
+      <c r="E199" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
+      <c r="A200" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B189" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C189" s="10">
-        <v>46302.739583333336</v>
-      </c>
-      <c r="D189" s="10">
-        <v>46302.770833333336</v>
-      </c>
-      <c r="E189" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="6" t="s">
+      <c r="B200" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C200" s="8">
+        <v>46305.625</v>
+      </c>
+      <c r="D200" s="8">
+        <v>46305.65625</v>
+      </c>
+      <c r="E200" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
+      <c r="A201" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C201" s="8">
+        <v>46305.666666666664</v>
+      </c>
+      <c r="D201" s="8">
+        <v>46305.697916666664</v>
+      </c>
+      <c r="E201" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C202" s="8">
+        <v>46312.625</v>
+      </c>
+      <c r="D202" s="8">
+        <v>46312.65625</v>
+      </c>
+      <c r="E202" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
+      <c r="A203" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C203" s="8">
+        <v>46312.666666666664</v>
+      </c>
+      <c r="D203" s="8">
+        <v>46312.697916666664</v>
+      </c>
+      <c r="E203" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
+      <c r="A204" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C204" s="8">
+        <v>46326.625</v>
+      </c>
+      <c r="D204" s="8">
+        <v>46326.65625</v>
+      </c>
+      <c r="E204" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
+      <c r="A205" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C205" s="8">
+        <v>46326.666666666664</v>
+      </c>
+      <c r="D205" s="8">
+        <v>46326.697916666664</v>
+      </c>
+      <c r="E205" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
+      <c r="A206" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B190" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C190" s="10">
-        <v>46309.708333333336</v>
-      </c>
-      <c r="D190" s="10">
-        <v>46309.739583333336</v>
-      </c>
-      <c r="E190" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C191" s="10">
-        <v>46309.739583333336</v>
-      </c>
-      <c r="D191" s="10">
-        <v>46309.770833333336</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="6" t="s">
+      <c r="B206" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C206" s="8">
+        <v>46299.416666666664</v>
+      </c>
+      <c r="D206" s="8">
+        <v>46299.458333333336</v>
+      </c>
+      <c r="E206" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
+      <c r="A207" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B192" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C192" s="10">
-        <v>46316.708333333336</v>
-      </c>
-      <c r="D192" s="10">
-        <v>46316.739583333336</v>
-      </c>
-      <c r="E192" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C193" s="10">
-        <v>46316.739583333336</v>
-      </c>
-      <c r="D193" s="10">
-        <v>46316.770833333336</v>
-      </c>
-      <c r="E193" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="6" t="s">
+      <c r="B207" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C207" s="8">
+        <v>46306.416666666664</v>
+      </c>
+      <c r="D207" s="8">
+        <v>46306.458333333336</v>
+      </c>
+      <c r="E207" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
+      <c r="A208" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B194" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C194" s="10">
-        <v>46323.708333333336</v>
-      </c>
-      <c r="D194" s="10">
-        <v>46323.739583333336</v>
-      </c>
-      <c r="E194" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C195" s="10">
-        <v>46323.739583333336</v>
-      </c>
-      <c r="D195" s="10">
-        <v>46323.770833333336</v>
-      </c>
-      <c r="E195" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C196" s="10">
-        <v>46297.666666666664</v>
-      </c>
-      <c r="D196" s="10">
-        <v>46297.70138888889</v>
-      </c>
-      <c r="E196" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C197" s="10">
-        <v>46304.666666666664</v>
-      </c>
-      <c r="D197" s="10">
-        <v>46304.70138888889</v>
-      </c>
-      <c r="E197" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C198" s="10">
-        <v>46311.666666666664</v>
-      </c>
-      <c r="D198" s="10">
-        <v>46311.70138888889</v>
-      </c>
-      <c r="E198" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C199" s="10">
-        <v>46318.666666666664</v>
-      </c>
-      <c r="D199" s="10">
-        <v>46318.70138888889</v>
-      </c>
-      <c r="E199" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="6" t="s">
+      <c r="B208" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C208" s="8">
+        <v>46313.416666666664</v>
+      </c>
+      <c r="D208" s="8">
+        <v>46313.458333333336</v>
+      </c>
+      <c r="E208" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
+      <c r="A209" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B200" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C200" s="10">
-        <v>46305.625</v>
-      </c>
-      <c r="D200" s="10">
-        <v>46305.65625</v>
-      </c>
-      <c r="E200" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C201" s="10">
-        <v>46305.666666666664</v>
-      </c>
-      <c r="D201" s="10">
-        <v>46305.697916666664</v>
-      </c>
-      <c r="E201" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="6" t="s">
+      <c r="B209" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C209" s="8">
+        <v>46298.395833333336</v>
+      </c>
+      <c r="D209" s="8">
+        <v>46298.458333333336</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
+      <c r="A210" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B202" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C202" s="10">
-        <v>46312.625</v>
-      </c>
-      <c r="D202" s="10">
-        <v>46312.65625</v>
-      </c>
-      <c r="E202" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C203" s="10">
-        <v>46312.666666666664</v>
-      </c>
-      <c r="D203" s="10">
-        <v>46312.697916666664</v>
-      </c>
-      <c r="E203" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="6" t="s">
+      <c r="B210" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C210" s="8">
+        <v>46299.583333333336</v>
+      </c>
+      <c r="D210" s="8">
+        <v>46299.645833333336</v>
+      </c>
+      <c r="E210" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="A211" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B204" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C204" s="10">
-        <v>46326.625</v>
-      </c>
-      <c r="D204" s="10">
-        <v>46326.65625</v>
-      </c>
-      <c r="E204" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C205" s="10">
-        <v>46326.666666666664</v>
-      </c>
-      <c r="D205" s="10">
-        <v>46326.697916666664</v>
-      </c>
-      <c r="E205" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C206" s="10">
-        <v>46299.416666666664</v>
-      </c>
-      <c r="D206" s="10">
-        <v>46299.458333333336</v>
-      </c>
-      <c r="E206" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C207" s="10">
-        <v>46306.416666666664</v>
-      </c>
-      <c r="D207" s="10">
-        <v>46306.458333333336</v>
-      </c>
-      <c r="E207" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C208" s="10">
-        <v>46313.416666666664</v>
-      </c>
-      <c r="D208" s="10">
-        <v>46313.458333333336</v>
-      </c>
-      <c r="E208" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C209" s="10">
-        <v>46298.395833333336</v>
-      </c>
-      <c r="D209" s="10">
-        <v>46298.458333333336</v>
-      </c>
-      <c r="E209" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C210" s="10">
-        <v>46299.583333333336</v>
-      </c>
-      <c r="D210" s="10">
-        <v>46299.645833333336</v>
-      </c>
-      <c r="E210" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C211" s="10">
+      <c r="B211" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C211" s="8">
         <v>46312.395833333336</v>
       </c>
-      <c r="D211" s="10">
+      <c r="D211" s="8">
         <v>46312.458333333336</v>
       </c>
-      <c r="E211" s="6" t="s">
-        <v>14</v>
+      <c r="E211" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C212" s="10">
+      <c r="A212" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212" s="8">
         <v>46313.583333333336</v>
       </c>
-      <c r="D212" s="10">
+      <c r="D212" s="8">
         <v>46313.645833333336</v>
       </c>
-      <c r="E212" s="6" t="s">
-        <v>31</v>
+      <c r="E212" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B213" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C213" s="10">
+      <c r="A213" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C213" s="8">
         <v>46319.5</v>
       </c>
-      <c r="D213" s="10">
+      <c r="D213" s="8">
         <v>46319.645833333336</v>
       </c>
-      <c r="E213" s="6" t="s">
-        <v>67</v>
+      <c r="E213" s="4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B214" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C214" s="10">
+      <c r="A214" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C214" s="8">
         <v>46320.375</v>
       </c>
-      <c r="D214" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E214" s="6" t="s">
-        <v>69</v>
+      <c r="D214" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B215" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C215" s="10">
+      <c r="A215" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C215" s="8">
         <v>46326.395833333336</v>
       </c>
-      <c r="D215" s="10">
+      <c r="D215" s="8">
         <v>46326.458333333336</v>
       </c>
-      <c r="E215" s="6" t="s">
-        <v>70</v>
+      <c r="E215" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1"/>
@@ -11493,30 +11501,28 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5">
         <v>46259.6666666667</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <v>46259.8333333333</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="7">
-        <v>46369.666666666664</v>
-      </c>
+      <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="7"/>
       <c r="D3" s="7">
         <v>46370.666666666664</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>16</v>
+      <c r="E3" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -12502,4 +12508,44 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="8">
+        <v>46350.333333333336</v>
+      </c>
+      <c r="D2" s="8">
+        <v>46350.708333333336</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>